--- a/numerical-workflows/v2/framework/06_最终配置/任务/Task.xlsx
+++ b/numerical-workflows/v2/framework/06_最终配置/任务/Task.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="Task" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Task" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -13058,12 +13058,12 @@
       </c>
       <c r="C192" s="66" t="inlineStr">
         <is>
-          <t>1个舱室达到2级</t>
+          <t>2个舱室达到2级</t>
         </is>
       </c>
       <c r="D192" s="66" t="inlineStr">
         <is>
-          <t>1个舱室达到2级</t>
+          <t>2个舱室达到2级</t>
         </is>
       </c>
       <c r="E192" s="66" t="n"/>
@@ -13650,12 +13650,12 @@
       </c>
       <c r="C202" s="66" t="inlineStr">
         <is>
-          <t>2个舱室达到2级</t>
+          <t>3个舱室达到2级</t>
         </is>
       </c>
       <c r="D202" s="66" t="inlineStr">
         <is>
-          <t>2个舱室达到2级</t>
+          <t>3个舱室达到2级</t>
         </is>
       </c>
       <c r="E202" s="70" t="n"/>
@@ -14124,12 +14124,12 @@
       </c>
       <c r="C210" s="66" t="inlineStr">
         <is>
-          <t>1个舱室达到3级</t>
+          <t>2个舱室达到3级</t>
         </is>
       </c>
       <c r="D210" s="66" t="inlineStr">
         <is>
-          <t>1个舱室达到3级</t>
+          <t>2个舱室达到3级</t>
         </is>
       </c>
       <c r="E210" s="70" t="n"/>
@@ -14659,12 +14659,12 @@
       </c>
       <c r="C219" s="66" t="inlineStr">
         <is>
-          <t>2个舱室达到3级</t>
+          <t>3个舱室达到3级</t>
         </is>
       </c>
       <c r="D219" s="66" t="inlineStr">
         <is>
-          <t>2个舱室达到3级</t>
+          <t>3个舱室达到3级</t>
         </is>
       </c>
       <c r="E219" s="70" t="n"/>
@@ -17448,12 +17448,12 @@
       </c>
       <c r="C266" s="68" t="inlineStr">
         <is>
-          <t>累计击败BOSS敌人3个</t>
+          <t>加一个好友</t>
         </is>
       </c>
       <c r="D266" s="68" t="inlineStr">
         <is>
-          <t>累计击败BOSS敌人3个</t>
+          <t>加一个好友</t>
         </is>
       </c>
       <c r="E266" s="70" t="n"/>
